--- a/templates/summary_template.xlsx
+++ b/templates/summary_template.xlsx
@@ -1155,7 +1155,7 @@
       <x:c r="C10" s="49" t="n"/>
       <x:c r="D10" s="28" t="n"/>
       <x:c r="E10" s="41" t="str">
-        <x:f>IF(AND(C10&lt;&gt;0,F10&lt;&gt;0),F10/C10*100,"")</x:f>
+        <x:f>IF(AND(C10&lt;&gt;0,F10&lt;&gt;0),F10/C10,"")</x:f>
       </x:c>
       <x:c r="F10" s="42" t="n"/>
       <x:c r="G10" s="43" t="n"/>
@@ -1166,7 +1166,7 @@
       </x:c>
       <x:c r="J10" s="28" t="n"/>
       <x:c r="K10" s="44" t="str">
-        <x:f>IF(AND(C10&lt;&gt;0,L10&lt;&gt;0),L10/C10*100,"")</x:f>
+        <x:f>IF(AND(C10&lt;&gt;0,L10&lt;&gt;0),L10/C10,"")</x:f>
       </x:c>
       <x:c r="L10" s="45" t="n"/>
       <x:c r="M10" s="46" t="n"/>
